--- a/nablarch_sample_aws/アプリケーション方式設計書_4バッチ処理方式_4.1.都度起動バッチ_AWS.xlsx
+++ b/nablarch_sample_aws/アプリケーション方式設計書_4バッチ処理方式_4.1.都度起動バッチ_AWS.xlsx
@@ -3,13 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49C8B9D-056D-48EF-8569-8CA0A85B892C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5566F491-42E5-4B61-A7AE-4778909929A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.1.都度起動バッチ" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'4.1.都度起動バッチ'!$A$1:$AI$412</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -637,9 +640,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>1 つのイベントに応じてルールが複数回トリガーされた | Amazon EventBridge ユーザーガイド</t>
-  </si>
-  <si>
     <t>この問題に対応するため、本システムではLambdaを用いた方式を採用する。</t>
     <rPh sb="2" eb="4">
       <t>モンダイ</t>
@@ -681,9 +681,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>name | StartExecution | AWS Step Functions API Reference</t>
-  </si>
-  <si>
     <t>この仕様を利用することで、イベントが2回以上通知された場合のジョブネットの重複起動を防止する。</t>
     <rPh sb="2" eb="4">
       <t>シヨウ</t>
@@ -1064,10 +1061,6 @@
   </si>
   <si>
     <t>多重起動しているかどうかのチェックは、TaskステートでlistExecutions APIを呼び出して実施する。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>listExecutions | AWS Step Functions API Reference</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2365,6 +2358,17 @@
     <t>シェルスクリプトを指定する。</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>https://docs.aws.amazon.com/ja_jp/step-functions/latest/apireference/API_ListExecutions.html</t>
+  </si>
+  <si>
+    <t>https://docs.aws.amazon.com/ja_jp/eventbridge/latest/userguide/eb-troubleshooting.html#eb-rule-triggered-more-than-once</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://docs.aws.amazon.com/ja_jp/step-functions/latest/apireference/API_StartExecution.html#StepFunctions-StartExecution-request-name</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -2373,7 +2377,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2452,6 +2456,14 @@
       <u/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
       <name val="ＭＳ 明朝"/>
       <family val="1"/>
       <charset val="128"/>
@@ -2654,7 +2666,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2807,6 +2819,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -7293,43 +7308,43 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="57"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="58"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="58" t="s">
+      <c r="R1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
-      <c r="V1" s="59"/>
-      <c r="W1" s="59"/>
-      <c r="X1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="61"/>
       <c r="Y1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="61"/>
-      <c r="AB1" s="62"/>
-      <c r="AC1" s="62"/>
-      <c r="AD1" s="62"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="52"/>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="54"/>
+      <c r="AA1" s="62"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="64"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="54"/>
+      <c r="AH1" s="54"/>
+      <c r="AI1" s="55"/>
     </row>
     <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
@@ -7338,43 +7353,43 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="57"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="58"/>
       <c r="P2" s="8" t="s">
         <v>5</v>
       </c>
       <c r="Q2" s="9"/>
-      <c r="R2" s="64" t="s">
+      <c r="R2" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+      <c r="U2" s="66"/>
+      <c r="V2" s="66"/>
+      <c r="W2" s="66"/>
+      <c r="X2" s="67"/>
       <c r="Y2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="62"/>
-      <c r="AC2" s="62"/>
-      <c r="AD2" s="62"/>
-      <c r="AE2" s="63"/>
-      <c r="AF2" s="52"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="53"/>
-      <c r="AI2" s="54"/>
+      <c r="AA2" s="62"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
+      <c r="AD2" s="63"/>
+      <c r="AE2" s="64"/>
+      <c r="AF2" s="53"/>
+      <c r="AG2" s="54"/>
+      <c r="AH2" s="54"/>
+      <c r="AI2" s="55"/>
     </row>
     <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
@@ -7383,39 +7398,39 @@
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="70"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="69"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="69"/>
+      <c r="U3" s="69"/>
+      <c r="V3" s="69"/>
+      <c r="W3" s="69"/>
+      <c r="X3" s="70"/>
       <c r="Y3" s="12" t="s">
         <v>9</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="61"/>
-      <c r="AB3" s="62"/>
-      <c r="AC3" s="62"/>
-      <c r="AD3" s="62"/>
-      <c r="AE3" s="63"/>
-      <c r="AF3" s="52"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="54"/>
+      <c r="AA3" s="62"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="63"/>
+      <c r="AD3" s="63"/>
+      <c r="AE3" s="64"/>
+      <c r="AF3" s="53"/>
+      <c r="AG3" s="54"/>
+      <c r="AH3" s="54"/>
+      <c r="AI3" s="55"/>
     </row>
     <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -7552,7 +7567,7 @@
       <c r="F21" s="16"/>
       <c r="K21" s="16"/>
       <c r="O21" s="16" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AF21" s="17"/>
     </row>
@@ -7560,7 +7575,7 @@
       <c r="F22" s="16"/>
       <c r="K22" s="16"/>
       <c r="O22" s="16" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AF22" s="17"/>
     </row>
@@ -7862,44 +7877,44 @@
     </row>
     <row r="81" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="82" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E82" s="72" t="s">
+      <c r="E82" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="F82" s="72"/>
-      <c r="G82" s="72"/>
-      <c r="H82" s="72"/>
-      <c r="I82" s="72"/>
-      <c r="J82" s="72"/>
-      <c r="K82" s="72"/>
-      <c r="L82" s="72" t="s">
+      <c r="F82" s="73"/>
+      <c r="G82" s="73"/>
+      <c r="H82" s="73"/>
+      <c r="I82" s="73"/>
+      <c r="J82" s="73"/>
+      <c r="K82" s="73"/>
+      <c r="L82" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="M82" s="72"/>
-      <c r="N82" s="72"/>
-      <c r="O82" s="72"/>
-      <c r="P82" s="72"/>
-      <c r="Q82" s="72"/>
-      <c r="R82" s="72"/>
-      <c r="S82" s="72" t="s">
+      <c r="M82" s="73"/>
+      <c r="N82" s="73"/>
+      <c r="O82" s="73"/>
+      <c r="P82" s="73"/>
+      <c r="Q82" s="73"/>
+      <c r="R82" s="73"/>
+      <c r="S82" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="T82" s="72"/>
-      <c r="U82" s="72"/>
-      <c r="V82" s="72"/>
-      <c r="W82" s="72"/>
-      <c r="X82" s="72"/>
-      <c r="Y82" s="72"/>
-      <c r="Z82" s="72"/>
-      <c r="AA82" s="71" t="s">
+      <c r="T82" s="73"/>
+      <c r="U82" s="73"/>
+      <c r="V82" s="73"/>
+      <c r="W82" s="73"/>
+      <c r="X82" s="73"/>
+      <c r="Y82" s="73"/>
+      <c r="Z82" s="73"/>
+      <c r="AA82" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="AB82" s="71"/>
-      <c r="AC82" s="71"/>
-      <c r="AD82" s="71"/>
-      <c r="AE82" s="71"/>
-      <c r="AF82" s="71"/>
-      <c r="AG82" s="71"/>
-      <c r="AH82" s="71"/>
+      <c r="AB82" s="72"/>
+      <c r="AC82" s="72"/>
+      <c r="AD82" s="72"/>
+      <c r="AE82" s="72"/>
+      <c r="AF82" s="72"/>
+      <c r="AG82" s="72"/>
+      <c r="AH82" s="72"/>
     </row>
     <row r="83" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E83" s="19"/>
@@ -8531,12 +8546,12 @@
     </row>
     <row r="149" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E149" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="150" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E150" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="151" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -8620,7 +8635,7 @@
       <c r="G157" s="20"/>
       <c r="H157" s="21"/>
       <c r="I157" s="19" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J157" s="20"/>
       <c r="K157" s="20"/>
@@ -8647,7 +8662,7 @@
       <c r="G158" s="23"/>
       <c r="H158" s="24"/>
       <c r="I158" s="22" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J158" s="23"/>
       <c r="K158" s="23"/>
@@ -8693,26 +8708,26 @@
     <row r="164" spans="5:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="165" spans="5:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G165" s="38" t="s">
-        <v>72</v>
+        <v>239</v>
       </c>
     </row>
     <row r="166" spans="5:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="167" spans="5:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F167" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="168" spans="5:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F168" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="169" spans="5:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AO169" s="39"/>
     </row>
     <row r="170" spans="5:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G170" s="38" t="s">
-        <v>75</v>
+      <c r="G170" s="52" t="s">
+        <v>240</v>
       </c>
       <c r="AO170" s="39"/>
     </row>
@@ -8721,19 +8736,19 @@
     </row>
     <row r="172" spans="5:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F172" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AO172" s="39"/>
     </row>
     <row r="173" spans="5:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F173" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AO173" s="39"/>
     </row>
     <row r="174" spans="5:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F174" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AO174" s="39"/>
     </row>
@@ -8742,19 +8757,19 @@
     </row>
     <row r="176" spans="5:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F176" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AO176" s="39"/>
     </row>
     <row r="177" spans="6:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F177" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AO177" s="39"/>
     </row>
     <row r="178" spans="6:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F178" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AO178" s="39"/>
     </row>
@@ -8767,19 +8782,19 @@
         <v>4.1.3.2.1.</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AO180" s="39"/>
     </row>
     <row r="181" spans="6:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G181" s="40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H181" s="41"/>
       <c r="I181" s="41"/>
       <c r="J181" s="41"/>
       <c r="K181" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L181" s="50"/>
       <c r="M181" s="50"/>
@@ -8811,7 +8826,7 @@
       <c r="I182" s="32"/>
       <c r="J182" s="32"/>
       <c r="K182" s="33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L182" s="32"/>
       <c r="M182" s="32"/>
@@ -8837,13 +8852,13 @@
     </row>
     <row r="183" spans="6:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G183" s="19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H183" s="20"/>
       <c r="I183" s="20"/>
       <c r="J183" s="20"/>
       <c r="K183" s="19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L183" s="20"/>
       <c r="M183" s="20"/>
@@ -8873,7 +8888,7 @@
       <c r="I184" s="23"/>
       <c r="J184" s="23"/>
       <c r="K184" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L184" s="23"/>
       <c r="M184" s="23"/>
@@ -8899,13 +8914,13 @@
     </row>
     <row r="185" spans="6:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G185" s="33" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H185" s="32"/>
       <c r="I185" s="32"/>
       <c r="J185" s="32"/>
       <c r="K185" s="33" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L185" s="32"/>
       <c r="M185" s="32"/>
@@ -8931,13 +8946,13 @@
     </row>
     <row r="186" spans="6:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G186" s="33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H186" s="32"/>
       <c r="I186" s="32"/>
       <c r="J186" s="32"/>
       <c r="K186" s="33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L186" s="32"/>
       <c r="M186" s="32"/>
@@ -8963,13 +8978,13 @@
     </row>
     <row r="187" spans="6:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G187" s="33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H187" s="32"/>
       <c r="I187" s="32"/>
       <c r="J187" s="32"/>
       <c r="K187" s="33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L187" s="32"/>
       <c r="M187" s="32"/>
@@ -8995,13 +9010,13 @@
     </row>
     <row r="188" spans="6:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G188" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H188" s="20"/>
       <c r="I188" s="20"/>
       <c r="J188" s="20"/>
       <c r="K188" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L188" s="20"/>
       <c r="M188" s="20"/>
@@ -9028,7 +9043,7 @@
       <c r="G189" s="16"/>
       <c r="J189" s="48"/>
       <c r="K189" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L189" s="48"/>
       <c r="M189" s="48"/>
@@ -9057,7 +9072,7 @@
       <c r="I190" s="23"/>
       <c r="J190" s="23"/>
       <c r="K190" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L190" s="23"/>
       <c r="M190" s="23"/>
@@ -9082,13 +9097,13 @@
     </row>
     <row r="191" spans="6:41" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G191" s="33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H191" s="32"/>
       <c r="I191" s="32"/>
       <c r="J191" s="32"/>
       <c r="K191" s="33" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L191" s="32"/>
       <c r="M191" s="32"/>
@@ -9309,55 +9324,55 @@
         <v>4.1.3.3.</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="201" spans="5:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F201" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="202" spans="5:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F202" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="203" spans="5:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F203" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="204" spans="5:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="205" spans="5:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F205" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="206" spans="5:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="207" spans="5:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G207" s="38" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
     </row>
     <row r="208" spans="5:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="209" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F209" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="210" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F210" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="211" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F211" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="212" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F212" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="213" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -9367,45 +9382,45 @@
         <v>4.1.3.4.</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="215" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F215" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="216" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F216" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="217" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F217" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="218" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="219" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G219" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="220" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="221" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F221" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="222" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F222" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="223" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="224" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G224" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="225" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -9415,18 +9430,18 @@
         <v>4.1.3.5.</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="227" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E227" s="37"/>
       <c r="F227" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="228" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F228" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="229" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -9436,37 +9451,37 @@
         <v>4.1.3.6.</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="231" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E231" s="37"/>
       <c r="F231" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="232" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E232" s="37"/>
       <c r="F232" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="233" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E233" s="37"/>
       <c r="F233" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="234" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F234" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="235" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="236" spans="2:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F236" s="4"/>
       <c r="G236" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H236" s="4"/>
       <c r="I236" s="4"/>
@@ -9499,30 +9514,30 @@
     </row>
     <row r="237" spans="2:35" s="46" customFormat="1" ht="298.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F237" s="4"/>
-      <c r="G237" s="73" t="s">
-        <v>124</v>
-      </c>
-      <c r="H237" s="74"/>
-      <c r="I237" s="74"/>
-      <c r="J237" s="74"/>
-      <c r="K237" s="74"/>
-      <c r="L237" s="74"/>
-      <c r="M237" s="74"/>
-      <c r="N237" s="74"/>
-      <c r="O237" s="74"/>
-      <c r="P237" s="74"/>
-      <c r="Q237" s="74"/>
-      <c r="R237" s="74"/>
-      <c r="S237" s="74"/>
-      <c r="T237" s="74"/>
-      <c r="U237" s="74"/>
-      <c r="V237" s="74"/>
-      <c r="W237" s="74"/>
-      <c r="X237" s="74"/>
-      <c r="Y237" s="74"/>
-      <c r="Z237" s="74"/>
-      <c r="AA237" s="74"/>
-      <c r="AB237" s="75"/>
+      <c r="G237" s="74" t="s">
+        <v>121</v>
+      </c>
+      <c r="H237" s="75"/>
+      <c r="I237" s="75"/>
+      <c r="J237" s="75"/>
+      <c r="K237" s="75"/>
+      <c r="L237" s="75"/>
+      <c r="M237" s="75"/>
+      <c r="N237" s="75"/>
+      <c r="O237" s="75"/>
+      <c r="P237" s="75"/>
+      <c r="Q237" s="75"/>
+      <c r="R237" s="75"/>
+      <c r="S237" s="75"/>
+      <c r="T237" s="75"/>
+      <c r="U237" s="75"/>
+      <c r="V237" s="75"/>
+      <c r="W237" s="75"/>
+      <c r="X237" s="75"/>
+      <c r="Y237" s="75"/>
+      <c r="Z237" s="75"/>
+      <c r="AA237" s="75"/>
+      <c r="AB237" s="76"/>
       <c r="AC237" s="4"/>
       <c r="AD237" s="4"/>
       <c r="AE237" s="4"/>
@@ -9538,7 +9553,7 @@
         <v>4.1.3.7.</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="240" spans="2:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -9546,7 +9561,7 @@
       <c r="C240"/>
       <c r="D240"/>
       <c r="F240" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G240" s="4"/>
       <c r="H240" s="4"/>
@@ -9583,7 +9598,7 @@
       <c r="C241"/>
       <c r="D241"/>
       <c r="F241" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G241" s="4"/>
       <c r="H241" s="4"/>
@@ -9652,7 +9667,7 @@
     </row>
     <row r="243" spans="2:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F243" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G243" s="4"/>
       <c r="H243" s="4"/>
@@ -9718,10 +9733,10 @@
     </row>
     <row r="245" spans="2:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F245" s="37" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
@@ -9754,10 +9769,10 @@
     </row>
     <row r="246" spans="2:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F246" s="37" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G246" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
@@ -9790,10 +9805,10 @@
     </row>
     <row r="247" spans="2:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F247" s="37" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
@@ -9858,7 +9873,7 @@
     </row>
     <row r="249" spans="2:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F249" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G249" s="4"/>
       <c r="H249" s="4"/>
@@ -9926,7 +9941,7 @@
       <c r="F251" s="4"/>
       <c r="G251" s="4"/>
       <c r="H251" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I251" s="4"/>
       <c r="J251" s="4"/>
@@ -9961,7 +9976,7 @@
       <c r="G252" s="4"/>
       <c r="H252" s="4"/>
       <c r="I252" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J252" s="4"/>
       <c r="K252" s="4"/>
@@ -10027,7 +10042,7 @@
       <c r="G254" s="4"/>
       <c r="H254" s="4"/>
       <c r="I254" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J254" s="4"/>
       <c r="K254" s="4"/>
@@ -10060,7 +10075,7 @@
       <c r="F255" s="4"/>
       <c r="G255" s="4"/>
       <c r="H255" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I255" s="4"/>
       <c r="J255" s="4"/>
@@ -10124,7 +10139,7 @@
     </row>
     <row r="257" spans="6:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F257" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G257" s="4"/>
       <c r="H257" s="4"/>
@@ -10158,7 +10173,7 @@
     </row>
     <row r="258" spans="6:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F258" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G258" s="4"/>
       <c r="H258" s="4"/>
@@ -10224,7 +10239,7 @@
     </row>
     <row r="260" spans="6:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F260" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G260" s="4"/>
       <c r="H260" s="4"/>
@@ -10258,7 +10273,7 @@
     </row>
     <row r="261" spans="6:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F261" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G261" s="4"/>
       <c r="H261" s="4"/>
@@ -10325,7 +10340,7 @@
     <row r="263" spans="6:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F263" s="4"/>
       <c r="G263" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H263" s="4"/>
       <c r="I263" s="4"/>
@@ -10358,30 +10373,30 @@
     </row>
     <row r="264" spans="6:35" s="46" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F264" s="4"/>
-      <c r="G264" s="73" t="s">
-        <v>144</v>
-      </c>
-      <c r="H264" s="74"/>
-      <c r="I264" s="74"/>
-      <c r="J264" s="74"/>
-      <c r="K264" s="74"/>
-      <c r="L264" s="74"/>
-      <c r="M264" s="74"/>
-      <c r="N264" s="74"/>
-      <c r="O264" s="74"/>
-      <c r="P264" s="74"/>
-      <c r="Q264" s="74"/>
-      <c r="R264" s="74"/>
-      <c r="S264" s="74"/>
-      <c r="T264" s="74"/>
-      <c r="U264" s="74"/>
-      <c r="V264" s="74"/>
-      <c r="W264" s="74"/>
-      <c r="X264" s="74"/>
-      <c r="Y264" s="74"/>
-      <c r="Z264" s="74"/>
-      <c r="AA264" s="74"/>
-      <c r="AB264" s="75"/>
+      <c r="G264" s="74" t="s">
+        <v>141</v>
+      </c>
+      <c r="H264" s="75"/>
+      <c r="I264" s="75"/>
+      <c r="J264" s="75"/>
+      <c r="K264" s="75"/>
+      <c r="L264" s="75"/>
+      <c r="M264" s="75"/>
+      <c r="N264" s="75"/>
+      <c r="O264" s="75"/>
+      <c r="P264" s="75"/>
+      <c r="Q264" s="75"/>
+      <c r="R264" s="75"/>
+      <c r="S264" s="75"/>
+      <c r="T264" s="75"/>
+      <c r="U264" s="75"/>
+      <c r="V264" s="75"/>
+      <c r="W264" s="75"/>
+      <c r="X264" s="75"/>
+      <c r="Y264" s="75"/>
+      <c r="Z264" s="75"/>
+      <c r="AA264" s="75"/>
+      <c r="AB264" s="76"/>
       <c r="AC264" s="4"/>
       <c r="AD264" s="4"/>
       <c r="AE264" s="4"/>
@@ -10424,7 +10439,7 @@
     </row>
     <row r="266" spans="6:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F266" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G266" s="4"/>
       <c r="H266" s="4"/>
@@ -10458,7 +10473,7 @@
     </row>
     <row r="267" spans="6:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F267" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G267" s="4"/>
       <c r="H267" s="4"/>
@@ -10525,7 +10540,7 @@
     <row r="269" spans="6:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F269" s="4"/>
       <c r="G269" s="47" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H269" s="4"/>
       <c r="I269" s="4"/>
@@ -10559,7 +10574,7 @@
     <row r="270" spans="6:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F270" s="4"/>
       <c r="G270" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H270" s="4"/>
       <c r="I270" s="4"/>
@@ -10624,7 +10639,7 @@
     </row>
     <row r="272" spans="6:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F272" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G272" s="4"/>
       <c r="H272" s="4"/>
@@ -10658,7 +10673,7 @@
     </row>
     <row r="273" spans="4:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F273" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G273" s="4"/>
       <c r="H273" s="4"/>
@@ -10692,7 +10707,7 @@
     </row>
     <row r="274" spans="4:35" s="46" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F274" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G274" s="4"/>
       <c r="H274" s="4"/>
@@ -10760,7 +10775,7 @@
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
       <c r="F276" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G276" s="4"/>
       <c r="H276" s="4"/>
@@ -10794,7 +10809,7 @@
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
       <c r="F277" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G277" s="4"/>
       <c r="H277" s="4"/>
@@ -10828,7 +10843,7 @@
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
       <c r="F278" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G278" s="4"/>
       <c r="H278" s="4"/>
@@ -10887,27 +10902,27 @@
         <v>4.1.4.</v>
       </c>
       <c r="E280" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="281" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E281" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="282" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E282" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="283" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E283" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="284" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E284" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="285" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -10958,32 +10973,32 @@
         <v>4.1.5.</v>
       </c>
       <c r="E327" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="328" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E328" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="329" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E329" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="330" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E330" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="331" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E331" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="332" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E332" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="333" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -10993,7 +11008,7 @@
         <v>4.1.6.</v>
       </c>
       <c r="E334" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="335" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -11002,17 +11017,17 @@
         <v>4.1.6.1.</v>
       </c>
       <c r="F335" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="336" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F336" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="337" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F337" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="338" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11022,12 +11037,12 @@
         <v>4.1.6.2.</v>
       </c>
       <c r="F339" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="340" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F340" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="341" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11037,17 +11052,17 @@
         <v>4.1.6.3.</v>
       </c>
       <c r="F342" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="343" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F343" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="344" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F344" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="345" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11057,7 +11072,7 @@
         <v>4.1.7.</v>
       </c>
       <c r="E346" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="347" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -11066,22 +11081,22 @@
         <v>4.1.7.1.</v>
       </c>
       <c r="F347" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="348" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F348" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="349" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F349" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="350" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F350" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="351" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11091,23 +11106,23 @@
         <v>4.1.7.2.</v>
       </c>
       <c r="F352" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="353" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E353" s="15"/>
       <c r="F353" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="354" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F354" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="355" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F355" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="356" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11117,17 +11132,17 @@
         <v>4.1.8.</v>
       </c>
       <c r="E357" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="358" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E358" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="359" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E359" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="360" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11137,7 +11152,7 @@
         <v>4.1.9.</v>
       </c>
       <c r="E361" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="362" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -11147,50 +11162,50 @@
         <v>4.1.9.1.</v>
       </c>
       <c r="F362" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="363" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F363" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="364" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="365" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F365" s="36" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G365" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="366" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G366" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="367" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G367" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="368" spans="4:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G368" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="369" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="370" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F370" s="36" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G370" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="371" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G371" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="372" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11200,7 +11215,7 @@
         <v>4.1.9.2.</v>
       </c>
       <c r="F373" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="374" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11210,22 +11225,22 @@
         <v>4.1.9.2.1.</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="376" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G376" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="377" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G377" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="378" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G378" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="379" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11235,27 +11250,27 @@
         <v>4.1.9.2.2.</v>
       </c>
       <c r="G380" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="381" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G381" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="382" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G382" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="383" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G383" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="384" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G384" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="385" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11265,22 +11280,22 @@
         <v>4.1.9.2.3.</v>
       </c>
       <c r="G386" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="387" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G387" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="388" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G388" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="389" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G389" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="390" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11290,38 +11305,38 @@
         <v>4.1.9.3.</v>
       </c>
       <c r="F391" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="392" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F392" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="393" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F393" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="394" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F394" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="395" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="396" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F396" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="397" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F397" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="398" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F398" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="399" spans="5:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -11331,29 +11346,29 @@
         <v>4.1.9.4.</v>
       </c>
       <c r="F400" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="401" spans="6:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F401" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="402" spans="6:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F402" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="403" spans="6:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="404" spans="6:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F404" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="405" spans="6:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="406" spans="6:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F406" s="25" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G406" s="26"/>
       <c r="H406" s="26"/>
@@ -11382,12 +11397,12 @@
     </row>
     <row r="407" spans="6:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F407" s="31" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G407" s="32"/>
       <c r="H407" s="32"/>
       <c r="I407" s="33" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J407" s="32"/>
       <c r="K407" s="32"/>
@@ -11411,17 +11426,17 @@
     </row>
     <row r="408" spans="6:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F408" s="30" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I408" s="16" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AB408" s="17"/>
     </row>
     <row r="409" spans="6:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F409" s="16"/>
       <c r="I409" s="16" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AB409" s="17"/>
     </row>
@@ -11433,7 +11448,7 @@
     <row r="411" spans="6:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F411" s="16"/>
       <c r="I411" s="16" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AB411" s="17"/>
     </row>
@@ -11442,7 +11457,7 @@
       <c r="G412" s="23"/>
       <c r="H412" s="23"/>
       <c r="I412" s="22" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J412" s="23"/>
       <c r="K412" s="23"/>
@@ -12158,12 +12173,12 @@
   <phoneticPr fontId="2"/>
   <hyperlinks>
     <hyperlink ref="G165" r:id="rId1" location="eb-rule-triggered-more-than-once" xr:uid="{4BEAB959-9CE7-48EB-BEAB-E571280C2DC0}"/>
-    <hyperlink ref="G170" r:id="rId2" location="StepFunctions-StartExecution-request-name" xr:uid="{DE4F8F7E-285D-4C0C-ADEE-CFF661993E7A}"/>
-    <hyperlink ref="G207" r:id="rId3" xr:uid="{42556E5D-BC1B-49CF-BC97-835B976F6EA4}"/>
+    <hyperlink ref="G207" r:id="rId2" xr:uid="{42556E5D-BC1B-49CF-BC97-835B976F6EA4}"/>
+    <hyperlink ref="G170" r:id="rId3" location="StepFunctions-StartExecution-request-name" xr:uid="{DE4F8F7E-285D-4C0C-ADEE-CFF661993E7A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId4"/>
-  <rowBreaks count="12" manualBreakCount="12">
+  <rowBreaks count="11" manualBreakCount="11">
     <brk id="31" max="34" man="1"/>
     <brk id="77" max="34" man="1"/>
     <brk id="112" max="34" man="1"/>
@@ -12175,7 +12190,6 @@
     <brk id="279" max="34" man="1"/>
     <brk id="360" max="34" man="1"/>
     <brk id="390" max="34" man="1"/>
-    <brk id="238" max="34" man="1"/>
   </rowBreaks>
   <drawing r:id="rId5"/>
 </worksheet>
